--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96609</v>
+        <v>96611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96611</v>
+        <v>96612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96612</v>
+        <v>96613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96613</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96623</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2023 artfynd.xlsx
+++ b/artfynd/A 9110-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131361922</v>
       </c>
       <c r="B2" t="n">
-        <v>96634</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
